--- a/reports/二级子公司D_利润表_2025-04.xlsx
+++ b/reports/二级子公司D_利润表_2025-04.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>83368358</v>
+        <v>85071151</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>81533677</v>
+        <v>81431594</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>305318525</v>
+        <v>304674071</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>280586</v>
+        <v>281372</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1052844</v>
+        <v>1055993</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>239079</v>
+        <v>240731</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>902369</v>
+        <v>905637</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>201030</v>
+        <v>200132</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>752017</v>
+        <v>754638</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>178942</v>
+        <v>179668</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>676794</v>
+        <v>678704</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>100594</v>
+        <v>99598</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>375997</v>
+        <v>376611</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>79573</v>
+        <v>79560</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>300806</v>
+        <v>300844</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>82288554</v>
+        <v>83990090</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>80453873</v>
+        <v>80350533</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4502203</v>
+        <v>4482281</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>16919253</v>
+        <v>16862120</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>350532</v>
+        <v>349393</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>1316056</v>
+        <v>1311235</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>597984</v>
+        <v>600465</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>2255916</v>
+        <v>2248816</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>72346865</v>
+        <v>72226548</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>270727356</v>
+        <v>270127871</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1193123</v>
+        <v>1205958</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4511937</v>
+        <v>4508367</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>402398</v>
+        <v>402364</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1503999</v>
+        <v>1505080</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1988835</v>
+        <v>2011630</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>7520116</v>
+        <v>7535913</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>502269</v>
+        <v>502348</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>1879948</v>
+        <v>1885904</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1794638</v>
+        <v>1804953</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>6768257</v>
+        <v>6792454</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>40043</v>
+        <v>40013</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>159992</v>
+        <v>160562</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1077664</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>4071680</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>716927</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>2711090</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>54795112</v>
+        <v>58136900</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>49182239</v>
+        <v>48642385</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>48287436</v>
+        <v>47745694</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>180480670</v>
+        <v>179982618</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>894803</v>
+        <v>896691</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>3384038</v>
+        <v>3372210</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1797465</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>6743641</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>576638</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2159087</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>361234</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1350865</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>434223</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1623337</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>325931</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1219358</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>217236</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>814011</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>180806</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>678992</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>855033</v>
+        <v>852080</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>3196026</v>
+        <v>3207596</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>646160</v>
+        <v>649990</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2444017</v>
+        <v>2452260</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>502613</v>
+        <v>498763</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>1879960</v>
+        <v>1884769</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3784976</v>
+        <v>3782905</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>14288467</v>
+        <v>14305818</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>150335</v>
+        <v>149140</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>599976</v>
+        <v>563851</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>319916</v>
+        <v>318094</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1280056</v>
+        <v>1278096</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>359373</v>
+        <v>318094</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1439938</v>
+        <v>1278096</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>40142</v>
+        <v>39864</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>160006</v>
+        <v>159448</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>161825</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>645668</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>315453</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1180885</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>108400</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>431110</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>81430</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>323786</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>135808</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>540464</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>452525</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1696118</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>72306</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>288922</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>54115</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>216780</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>89968</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>361221</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>62825</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>252648</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>44788</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>180234</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>35790</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>143970</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>26841</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>107820</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>27493442</v>
+        <v>26963408</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31560320</v>
+        <v>29895920</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>179866</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>674417</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>45079</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>179461</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>70176</v>
+        <v>70277</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>280012</v>
+        <v>279470</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>27423266</v>
+        <v>27072997</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2513425</v>
+        <v>2515000</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>10000206</v>
+        <v>10010564</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>24909841</v>
+        <v>24557997</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>24909841</v>
+        <v>24557997</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>24909841</v>
+        <v>24557997</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>24909841</v>
+        <v>24557997</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>24909841</v>
+        <v>24557997</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
